--- a/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-task.xlsx
+++ b/tiflow/develop/2.0.0-ballot.1/StructureDefinition-ti-task.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/tiflow-core/StructureDefinition/ti-task</t>
+    <t>https://gematik.de/fhir/tiflow/StructureDefinition/ti-task</t>
   </si>
   <si>
     <t>Version</t>
